--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common Master-Detail_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common Master-Detail_report.xlsx
@@ -227,7 +227,7 @@
         <xdr:cNvPr id="3" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9035b987-3b3a-4103-ab2f-a55ed7ee19c7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ae726678-7780-436f-b1ad-1e75e72e85f0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -312,7 +312,7 @@
         <xdr:cNvPr id="4" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{d5f82702-63f0-4bff-884f-f8317dbd451a}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ae6734ea-8cab-4b50-9d5c-922b7acac0b9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -397,7 +397,7 @@
         <xdr:cNvPr id="5" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{eab7e2d2-f45d-4ee6-8a65-bab6e1dac8f6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{fa41ca38-2de3-4951-ad77-c031a13e3a80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common Master-Detail_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common Master-Detail_report.xlsx
@@ -227,7 +227,7 @@
         <xdr:cNvPr id="3" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ae726678-7780-436f-b1ad-1e75e72e85f0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5f44ee3e-eeaa-4bb2-9bcc-972f3a3ce862}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -312,7 +312,7 @@
         <xdr:cNvPr id="4" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ae6734ea-8cab-4b50-9d5c-922b7acac0b9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6427634d-ee93-4538-854b-46014b86263c}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -397,7 +397,7 @@
         <xdr:cNvPr id="5" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{fa41ca38-2de3-4951-ad77-c031a13e3a80}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a00e989d-5150-400f-91dc-d6c3e4768770}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common Master-Detail_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common Master-Detail_report.xlsx
@@ -227,7 +227,7 @@
         <xdr:cNvPr id="3" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5f44ee3e-eeaa-4bb2-9bcc-972f3a3ce862}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{b337cead-8ffe-454d-92ce-89693b30e9bb}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -312,7 +312,7 @@
         <xdr:cNvPr id="4" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6427634d-ee93-4538-854b-46014b86263c}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a36b0d5b-ad8c-4e63-ad26-af5ba5bb167d}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -397,7 +397,7 @@
         <xdr:cNvPr id="5" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a00e989d-5150-400f-91dc-d6c3e4768770}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7d1279ed-08fa-4e89-ac08-6e10b215bf5b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
